--- a/input/timetable/Медиакоммуникации. xlsx.xlsx
+++ b/input/timetable/Медиакоммуникации. xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
   <si>
     <t>пара</t>
   </si>
@@ -237,7 +237,10 @@
     <t>Медиасистема России (пр), К429//</t>
   </si>
   <si>
-    <t>Основы программного и аппаратного обеспечения медиакоммуникации (пр). К406</t>
+    <t>Основы программного и аппаратного обеспечения медиакоммуникации (пр). К433</t>
+  </si>
+  <si>
+    <t>Съемка и монтаж видео (пр), К433</t>
   </si>
 </sst>
 </file>
@@ -1093,47 +1096,14 @@
     <xf numFmtId="16" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1144,10 +1114,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1156,29 +1127,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1198,9 +1146,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1219,58 +1164,74 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1281,10 +1242,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1304,6 +1261,52 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1721,10 +1724,10 @@
       <c r="A8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="62"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="44" t="s">
         <v>43</v>
       </c>
@@ -1736,12 +1739,12 @@
       <c r="A9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
@@ -1764,48 +1767,48 @@
       <c r="B11" s="22">
         <v>1</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="101"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="60"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="24">
         <v>2</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="65"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="97"/>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="25"/>
       <c r="B14" s="26">
         <v>4</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="61"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="93"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -1814,46 +1817,46 @@
       <c r="B15" s="28">
         <v>1</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="112"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="24">
         <v>2</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C16" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="75"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="83"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="109"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="26">
         <v>4</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="80"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="106"/>
     </row>
     <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
@@ -1862,48 +1865,48 @@
       <c r="B19" s="28">
         <v>2</v>
       </c>
-      <c r="C19" s="108" t="s">
+      <c r="C19" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="110"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="23"/>
       <c r="B20" s="22">
         <v>4</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="75"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="63"/>
     </row>
     <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="23"/>
       <c r="B21" s="24">
         <v>5</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67" t="s">
+      <c r="D21" s="54"/>
+      <c r="E21" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="68"/>
+      <c r="F21" s="55"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="26">
         <v>6</v>
       </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="72"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="101"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="27" t="s">
@@ -1912,46 +1915,46 @@
       <c r="B23" s="28">
         <v>1</v>
       </c>
-      <c r="C23" s="76"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="111" t="s">
+      <c r="C23" s="102"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="112"/>
+      <c r="F23" s="57"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="23"/>
       <c r="B24" s="24">
         <v>2</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="68"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="55"/>
     </row>
     <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="23"/>
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="55"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="26">
         <v>4</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="27" t="s">
@@ -1960,44 +1963,44 @@
       <c r="B27" s="28">
         <v>3</v>
       </c>
-      <c r="C27" s="90"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="92"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="69"/>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="32"/>
       <c r="B28" s="24">
         <v>4</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="55"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="32"/>
       <c r="B29" s="24">
         <v>5</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="55"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="33"/>
       <c r="B30" s="26">
         <v>6</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="95"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="72"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="34" t="s">
@@ -2006,92 +2009,92 @@
       <c r="B31" s="22">
         <v>1</v>
       </c>
-      <c r="C31" s="105" t="s">
+      <c r="C31" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="107"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="81"/>
     </row>
     <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="35"/>
       <c r="B32" s="24">
         <v>3</v>
       </c>
-      <c r="C32" s="102" t="s">
+      <c r="C32" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="104"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="78"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="36"/>
       <c r="B33" s="31">
         <v>4</v>
       </c>
-      <c r="C33" s="53" t="s">
+      <c r="C33" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="55"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="87"/>
     </row>
     <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="37"/>
       <c r="B34" s="38"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="58"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="39"/>
       <c r="B35" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="99" t="s">
+      <c r="C35" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="100"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="101"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="60"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="35"/>
       <c r="B36" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="96" t="s">
+      <c r="C36" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="97"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="98"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="36"/>
       <c r="B37" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="96" t="s">
+      <c r="C37" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="98"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="75"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="41"/>
       <c r="B38" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="87" t="s">
+      <c r="C38" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="89"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="66"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
@@ -2111,22 +2114,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
@@ -2143,6 +2130,22 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C20:F20"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>
@@ -2259,10 +2262,10 @@
       <c r="A8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="62"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="44" t="s">
         <v>45</v>
       </c>
@@ -2274,12 +2277,12 @@
       <c r="A9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
@@ -2302,46 +2305,46 @@
       <c r="B11" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="116" t="s">
+      <c r="C11" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="118"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="137"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="24">
         <v>4</v>
       </c>
-      <c r="C12" s="119" t="s">
+      <c r="C12" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="122"/>
-      <c r="E12" s="123" t="s">
+      <c r="D12" s="141"/>
+      <c r="E12" s="142" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="121"/>
+      <c r="F12" s="140"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>5</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="138" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="121"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="140"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="25"/>
       <c r="B14" s="24"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="115"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="134"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -2350,46 +2353,46 @@
       <c r="B15" s="28">
         <v>2</v>
       </c>
-      <c r="C15" s="124" t="s">
+      <c r="C15" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="127"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="24">
         <v>3</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C16" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="75"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>4</v>
       </c>
-      <c r="C17" s="127" t="s">
+      <c r="C17" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="129"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="26">
         <v>5</v>
       </c>
-      <c r="C18" s="130"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="132"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="130"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
@@ -2398,44 +2401,44 @@
       <c r="B19" s="28">
         <v>5</v>
       </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="133"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="131"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="23"/>
       <c r="B20" s="24">
         <v>6</v>
       </c>
-      <c r="C20" s="127"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="129"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
     </row>
     <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="23"/>
       <c r="B21" s="24">
         <v>7</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="68"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="55"/>
     </row>
     <row r="22" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="26">
         <v>8</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="87"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="27" t="s">
@@ -2444,44 +2447,44 @@
       <c r="B23" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="99" t="s">
+      <c r="C23" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="101"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
     </row>
     <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="23"/>
       <c r="B24" s="24"/>
-      <c r="C24" s="134"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="136"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="30"/>
       <c r="B25" s="24">
         <v>7</v>
       </c>
-      <c r="C25" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
+      <c r="C25" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="55"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="24">
         <v>8</v>
       </c>
-      <c r="C26" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68"/>
+      <c r="C26" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="55"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="27" t="s">
@@ -2490,44 +2493,44 @@
       <c r="B27" s="28">
         <v>5</v>
       </c>
-      <c r="C27" s="137"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="138"/>
-      <c r="F27" s="139"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="121"/>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="32"/>
       <c r="B28" s="24">
         <v>6</v>
       </c>
-      <c r="C28" s="140"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="142"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="124"/>
     </row>
     <row r="29" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="32"/>
       <c r="B29" s="24">
         <v>7</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="55"/>
     </row>
     <row r="30" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="33"/>
       <c r="B30" s="26">
         <v>8</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="55"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="87"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="34" t="s">
@@ -2536,92 +2539,92 @@
       <c r="B31" s="22">
         <v>1</v>
       </c>
-      <c r="C31" s="105" t="s">
+      <c r="C31" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="107"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="81"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="32"/>
       <c r="B32" s="22">
         <v>2</v>
       </c>
-      <c r="C32" s="102" t="s">
+      <c r="C32" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="104"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="78"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="35"/>
       <c r="B33" s="24">
         <v>3</v>
       </c>
-      <c r="C33" s="102" t="s">
+      <c r="C33" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="104"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="78"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="36"/>
       <c r="B34" s="31">
         <v>4</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="55"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="87"/>
     </row>
     <row r="35" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="37"/>
       <c r="B35" s="38"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="58"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="90"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="39"/>
       <c r="B36" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="105" t="s">
+      <c r="C36" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="107"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="81"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="35"/>
       <c r="B37" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="102" t="s">
+      <c r="C37" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="104"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="78"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="41"/>
       <c r="B38" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="87" t="s">
+      <c r="C38" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="89"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="66"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
@@ -2641,14 +2644,18 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
@@ -2660,18 +2667,14 @@
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6">

--- a/input/timetable/Медиакоммуникации. xlsx.xlsx
+++ b/input/timetable/Медиакоммуникации. xlsx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="94">
   <si>
     <t>пара</t>
   </si>
@@ -75,6 +75,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -117,12 +120,24 @@
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
+    <t>Шевкунов А.Н.</t>
+  </si>
+  <si>
+    <t>Бирюкова Н.С.</t>
+  </si>
+  <si>
     <t>Мировая художественная культура (лек)/(пр), К625</t>
   </si>
   <si>
     <t>Мировая художественная культура (пр), К625</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
     <t>Мировая художественная культура (лек), К625</t>
   </si>
   <si>
@@ -132,15 +147,30 @@
     <t>Физическая культура и спорт//Элективные дисциплины по физической культуре и спорту, С</t>
   </si>
   <si>
+    <t>Ташманова Н.В.</t>
+  </si>
+  <si>
     <t>Элективные дисциплины по физической культуре и спорту, С</t>
   </si>
   <si>
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Афян К.А.; Савш И.Ю.</t>
+  </si>
+  <si>
+    <t>Слободенюк М.А.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
+    <t>Дроздова А.А.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (пр), К433</t>
   </si>
   <si>
@@ -168,12 +198,33 @@
     <t xml:space="preserve"> Медиакоммуникации (ТО : 02.02.2026 - 06.06.2026)</t>
   </si>
   <si>
+    <t>Ситникова А.Ю.; Подлуцкая К.А.</t>
+  </si>
+  <si>
+    <t>Воробьева А.Д.</t>
+  </si>
+  <si>
+    <t>Бирюкова Н.С./Раздобреев О.В.</t>
+  </si>
+  <si>
+    <t>Раздобреев О.В.</t>
+  </si>
+  <si>
+    <t>Бедных О.Г.</t>
+  </si>
+  <si>
     <t>Элективные дисциплины по физической культуре и спорту, С*</t>
   </si>
   <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
@@ -183,6 +234,12 @@
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Конышев В.Ю.</t>
+  </si>
+  <si>
+    <t>Ищенко О.В./Раздобреев О.В.</t>
+  </si>
+  <si>
     <t>История России (пр), К413</t>
   </si>
   <si>
@@ -199,6 +256,12 @@
   </si>
   <si>
     <t>1-2.</t>
+  </si>
+  <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
+    <t>Плесовских И.Н.</t>
   </si>
   <si>
     <t>Съемка и монтаж видео (пр), К406</t>
@@ -341,7 +404,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,12 +423,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -482,6 +551,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -736,6 +818,19 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -872,6 +967,17 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -969,7 +1075,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1005,28 +1111,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1050,25 +1159,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1081,232 +1193,247 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1638,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" customWidth="1"/>
@@ -1647,10 +1774,11 @@
     <col min="4" max="4" width="18.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -1658,15 +1786,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1674,13 +1802,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1690,29 +1818,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="43"/>
+      <c r="C7" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="47"/>
       <c r="E7" s="10">
         <v>1</v>
       </c>
@@ -1720,35 +1848,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="94"/>
-      <c r="E8" s="44" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="81"/>
+      <c r="E8" s="48" t="s">
+        <v>53</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="98" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -1759,344 +1887,419 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="23">
         <v>1</v>
       </c>
-      <c r="C11" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>2</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
+        <v>3</v>
+      </c>
+      <c r="C13" s="85" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
+        <v>4</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="29">
+        <v>1</v>
+      </c>
+      <c r="C15" s="103" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
+        <v>2</v>
+      </c>
+      <c r="C16" s="92" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
+        <v>3</v>
+      </c>
+      <c r="C17" s="100" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27">
+        <v>4</v>
+      </c>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="49"/>
+    </row>
+    <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="29">
+        <v>2</v>
+      </c>
+      <c r="C19" s="127" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="56" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23">
+        <v>4</v>
+      </c>
+      <c r="C20" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>5</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="87"/>
+      <c r="G21" s="55" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
+        <v>6</v>
+      </c>
+      <c r="C22" s="89"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="49"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="29">
+        <v>1</v>
+      </c>
+      <c r="C23" s="95"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="130" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="131"/>
+      <c r="G23" s="56" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
+        <v>2</v>
+      </c>
+      <c r="C24" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="61" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
+        <v>4</v>
+      </c>
+      <c r="C26" s="69"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="54"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="29">
+        <v>3</v>
+      </c>
+      <c r="C27" s="109"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="35"/>
+      <c r="B28" s="25">
+        <v>4</v>
+      </c>
+      <c r="C28" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="97"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="35"/>
+      <c r="B29" s="25">
+        <v>5</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="61" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="36"/>
+      <c r="B30" s="27">
+        <v>6</v>
+      </c>
+      <c r="C30" s="112"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="33"/>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="23">
+        <v>1</v>
+      </c>
+      <c r="C31" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="125"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="38"/>
+      <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C32" s="121" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="32">
+        <v>4</v>
+      </c>
+      <c r="C33" s="72" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="58" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="42"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="43"/>
+      <c r="B35" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="38"/>
+      <c r="B36" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="115" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="39"/>
+      <c r="B37" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="115" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="58" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="45"/>
+      <c r="B38" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
-        <v>4</v>
-      </c>
-      <c r="C14" s="91" t="s">
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="93"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="28">
-        <v>1</v>
-      </c>
-      <c r="C15" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="112"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
-        <v>2</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
-        <v>3</v>
-      </c>
-      <c r="C17" s="107" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="109"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26">
-        <v>4</v>
-      </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="106"/>
-    </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="28">
-        <v>2</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="52"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="22">
-        <v>4</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="63"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>5</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="55"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
-        <v>6</v>
-      </c>
-      <c r="C22" s="99"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="101"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="28">
-        <v>1</v>
-      </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="57"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24">
-        <v>2</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="55"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
-        <v>3</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
-        <v>4</v>
-      </c>
-      <c r="C26" s="82"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="28">
-        <v>3</v>
-      </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32"/>
-      <c r="B28" s="24">
-        <v>4</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32"/>
-      <c r="B29" s="24">
-        <v>5</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="33"/>
-      <c r="B30" s="26">
-        <v>6</v>
-      </c>
-      <c r="C30" s="70"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72"/>
-    </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="22">
-        <v>1</v>
-      </c>
-      <c r="C31" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="81"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="35"/>
-      <c r="B32" s="24">
-        <v>3</v>
-      </c>
-      <c r="C32" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="36"/>
-      <c r="B33" s="31">
-        <v>4</v>
-      </c>
-      <c r="C33" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="87"/>
-    </row>
-    <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="39"/>
-      <c r="B35" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="60"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="35"/>
-      <c r="B36" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="75"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="36"/>
-      <c r="B37" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="73" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="75"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="41"/>
-      <c r="B38" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="66"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
         <v>15</v>
       </c>
@@ -2104,7 +2307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
         <v>16</v>
       </c>
@@ -2114,6 +2317,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
@@ -2130,22 +2349,6 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C20:F20"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>
@@ -2176,7 +2379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" customWidth="1"/>
@@ -2185,10 +2388,11 @@
     <col min="4" max="4" width="20.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2196,15 +2400,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -2212,13 +2416,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -2228,29 +2432,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="43"/>
+      <c r="C7" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="47"/>
       <c r="E7" s="10">
         <v>2</v>
       </c>
@@ -2258,35 +2462,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="94"/>
-      <c r="E8" s="44" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="81"/>
+      <c r="E8" s="48" t="s">
+        <v>55</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -2297,336 +2501,403 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>58</v>
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="C11" s="135" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D11" s="136"/>
       <c r="E11" s="136"/>
       <c r="F11" s="137"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="G11" s="34"/>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>4</v>
       </c>
       <c r="C12" s="138" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D12" s="141"/>
       <c r="E12" s="142" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F12" s="140"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="G12" s="57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>5</v>
       </c>
       <c r="C13" s="138" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D13" s="139"/>
       <c r="E13" s="139"/>
       <c r="F13" s="140"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="24"/>
+      <c r="G13" s="57" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="132"/>
       <c r="D14" s="133"/>
       <c r="E14" s="133"/>
       <c r="F14" s="134"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="G14" s="33"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="29">
         <v>2</v>
       </c>
-      <c r="C15" s="125" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="127"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="143" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="63" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="92" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="61" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
+        <v>4</v>
+      </c>
+      <c r="C17" s="146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="61" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27">
+        <v>5</v>
+      </c>
+      <c r="C18" s="149"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="53"/>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="29">
+        <v>5</v>
+      </c>
+      <c r="C19" s="95"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="51"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
+        <v>6</v>
+      </c>
+      <c r="C20" s="146"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="61"/>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>7</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
+        <v>8</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="52"/>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="154"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="52"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="31"/>
+      <c r="B25" s="25">
+        <v>7</v>
+      </c>
+      <c r="C25" s="85" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="25">
+        <v>8</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="68" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="29">
+        <v>5</v>
+      </c>
+      <c r="C27" s="156"/>
+      <c r="D27" s="157"/>
+      <c r="E27" s="157"/>
+      <c r="F27" s="158"/>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="35"/>
+      <c r="B28" s="25">
+        <v>6</v>
+      </c>
+      <c r="C28" s="159"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="52"/>
+    </row>
+    <row r="29" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="35"/>
+      <c r="B29" s="25">
+        <v>7</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="36"/>
+      <c r="B30" s="27">
+        <v>8</v>
+      </c>
+      <c r="C30" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="23">
+        <v>1</v>
+      </c>
+      <c r="C31" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="125"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="35"/>
+      <c r="B32" s="23">
+        <v>2</v>
+      </c>
+      <c r="C32" s="121" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="38"/>
+      <c r="B33" s="25">
+        <v>3</v>
+      </c>
+      <c r="C33" s="121" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="122"/>
+      <c r="E33" s="122"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="39"/>
+      <c r="B34" s="32">
         <v>4</v>
       </c>
-      <c r="C17" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="115"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26">
-        <v>5</v>
-      </c>
-      <c r="C18" s="128"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="130"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="28">
-        <v>5</v>
-      </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="131"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
-        <v>6</v>
-      </c>
-      <c r="C20" s="113"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="115"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>7</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="55"/>
-    </row>
-    <row r="22" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
-        <v>8</v>
-      </c>
-      <c r="C22" s="85" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="60"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="118"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="30"/>
-      <c r="B25" s="24">
-        <v>7</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="24">
-        <v>8</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="55"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="28">
-        <v>5</v>
-      </c>
-      <c r="C27" s="119"/>
-      <c r="D27" s="120"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="121"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32"/>
-      <c r="B28" s="24">
-        <v>6</v>
-      </c>
-      <c r="C28" s="122"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="124"/>
-    </row>
-    <row r="29" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32"/>
-      <c r="B29" s="24">
-        <v>7</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55"/>
-    </row>
-    <row r="30" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="33"/>
-      <c r="B30" s="26">
-        <v>8</v>
-      </c>
-      <c r="C30" s="85" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="87"/>
-    </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="22">
-        <v>1</v>
-      </c>
-      <c r="C31" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="81"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="32"/>
-      <c r="B32" s="22">
-        <v>2</v>
-      </c>
-      <c r="C32" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="35"/>
-      <c r="B33" s="24">
-        <v>3</v>
-      </c>
-      <c r="C33" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="78"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="31">
-        <v>4</v>
-      </c>
-      <c r="C34" s="85" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="87"/>
-    </row>
-    <row r="35" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="90"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="39"/>
-      <c r="B36" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="79" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="81"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="35"/>
-      <c r="B37" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="76" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="78"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="41"/>
-      <c r="B38" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="66"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="42"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="43"/>
+      <c r="B36" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="124" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="38"/>
+      <c r="B37" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="123"/>
+      <c r="G37" s="57" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="45"/>
+      <c r="B38" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="106" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="68" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
         <v>15</v>
       </c>
@@ -2634,7 +2905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
         <v>16</v>
       </c>
@@ -2644,18 +2915,14 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
@@ -2667,14 +2934,18 @@
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6">
